--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/153.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/153.xlsx
@@ -426,13 +426,13 @@
         <v>-0.5222669988938246</v>
       </c>
       <c r="E2">
-        <v>-14.29320194474751</v>
+        <v>-17.57678939076127</v>
       </c>
       <c r="F2">
-        <v>-2.654414854206424</v>
+        <v>-3.728215921311784</v>
       </c>
       <c r="G2">
-        <v>-6.195634158685732</v>
+        <v>-7.922864946162925</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.193760759828994</v>
       </c>
       <c r="E3">
-        <v>-15.74001769088014</v>
+        <v>-16.80703937893747</v>
       </c>
       <c r="F3">
-        <v>-3.136430248751817</v>
+        <v>-3.997360774155371</v>
       </c>
       <c r="G3">
-        <v>-5.94454252171417</v>
+        <v>-8.11093703824892</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.050956255228388</v>
       </c>
       <c r="E4">
-        <v>-14.55450395193811</v>
+        <v>-17.48810375579506</v>
       </c>
       <c r="F4">
-        <v>-3.491152081243816</v>
+        <v>-3.69655074897237</v>
       </c>
       <c r="G4">
-        <v>-6.296039694346288</v>
+        <v>-7.679298179202125</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.980164874900227</v>
       </c>
       <c r="E5">
-        <v>-15.20755518858425</v>
+        <v>-18.74138610826187</v>
       </c>
       <c r="F5">
-        <v>-3.209467402656649</v>
+        <v>-3.715205582883415</v>
       </c>
       <c r="G5">
-        <v>-5.887783218443365</v>
+        <v>-7.446172872872188</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.946779143847447</v>
       </c>
       <c r="E6">
-        <v>-16.9274967875415</v>
+        <v>-18.82015438515129</v>
       </c>
       <c r="F6">
-        <v>-3.716772854009511</v>
+        <v>-3.700646197411811</v>
       </c>
       <c r="G6">
-        <v>-6.040501994715484</v>
+        <v>-7.011283058105828</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.879338085796678</v>
       </c>
       <c r="E7">
-        <v>-16.94910213703209</v>
+        <v>-20.17227068283552</v>
       </c>
       <c r="F7">
-        <v>-3.351432179781026</v>
+        <v>-3.749248169668864</v>
       </c>
       <c r="G7">
-        <v>-6.000980702067665</v>
+        <v>-8.924215587062898</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.72017208548601</v>
       </c>
       <c r="E8">
-        <v>-19.54991797148737</v>
+        <v>-21.3659039756733</v>
       </c>
       <c r="F8">
-        <v>-3.607993303408686</v>
+        <v>-3.541584745461055</v>
       </c>
       <c r="G8">
-        <v>-5.845010970075982</v>
+        <v>-7.943876978700678</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.403982380022758</v>
       </c>
       <c r="E9">
-        <v>-19.70231923574151</v>
+        <v>-21.37850219036264</v>
       </c>
       <c r="F9">
-        <v>-2.990090035005854</v>
+        <v>-3.432424145854942</v>
       </c>
       <c r="G9">
-        <v>-4.899062308775711</v>
+        <v>-8.287051439847069</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.879231315488929</v>
       </c>
       <c r="E10">
-        <v>-20.75941450877403</v>
+        <v>-22.21772805041212</v>
       </c>
       <c r="F10">
-        <v>-3.234885856411552</v>
+        <v>-3.319968300720492</v>
       </c>
       <c r="G10">
-        <v>-5.121060871548158</v>
+        <v>-8.296006465530798</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.101488356036175</v>
       </c>
       <c r="E11">
-        <v>-22.47784359741271</v>
+        <v>-22.68449145180473</v>
       </c>
       <c r="F11">
-        <v>-2.957976715901525</v>
+        <v>-3.104614313545094</v>
       </c>
       <c r="G11">
-        <v>-5.032858006745356</v>
+        <v>-8.452300630985329</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.044277481215648</v>
       </c>
       <c r="E12">
-        <v>-22.05500639389451</v>
+        <v>-23.92111807687134</v>
       </c>
       <c r="F12">
-        <v>-2.967463179398385</v>
+        <v>-3.221253414063681</v>
       </c>
       <c r="G12">
-        <v>-5.355427632455322</v>
+        <v>-7.081930099913875</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.694628107897491</v>
       </c>
       <c r="E13">
-        <v>-21.81147864718402</v>
+        <v>-25.33908291510109</v>
       </c>
       <c r="F13">
-        <v>-2.897706360408639</v>
+        <v>-2.866833935673704</v>
       </c>
       <c r="G13">
-        <v>-4.454161404298596</v>
+        <v>-7.166527780624411</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.063005131255875</v>
       </c>
       <c r="E14">
-        <v>-23.06700259428463</v>
+        <v>-25.52784782563683</v>
       </c>
       <c r="F14">
-        <v>-2.273665717918465</v>
+        <v>-2.782713225919414</v>
       </c>
       <c r="G14">
-        <v>-3.080099614950853</v>
+        <v>-6.252320629954673</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.176733033299243</v>
       </c>
       <c r="E15">
-        <v>-24.61928197158189</v>
+        <v>-26.19985978295308</v>
       </c>
       <c r="F15">
-        <v>-2.206934925051145</v>
+        <v>-2.680977283344593</v>
       </c>
       <c r="G15">
-        <v>-4.628166988388228</v>
+        <v>-6.011415541607447</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.074167531406203</v>
       </c>
       <c r="E16">
-        <v>-25.98359797824278</v>
+        <v>-26.61004443009386</v>
       </c>
       <c r="F16">
-        <v>-2.056621032873952</v>
+        <v>-2.481160983543504</v>
       </c>
       <c r="G16">
-        <v>-3.26067663193594</v>
+        <v>-5.295056524001173</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.815151700765295</v>
       </c>
       <c r="E17">
-        <v>-26.02318136954382</v>
+        <v>-28.24701532828257</v>
       </c>
       <c r="F17">
-        <v>-1.168091790711327</v>
+        <v>-1.760341349016862</v>
       </c>
       <c r="G17">
-        <v>-2.207654996259021</v>
+        <v>-5.217699006385024</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.465073871824886</v>
       </c>
       <c r="E18">
-        <v>-27.44530787538663</v>
+        <v>-29.05953677710882</v>
       </c>
       <c r="F18">
-        <v>-1.83992260540381</v>
+        <v>-2.585811122641374</v>
       </c>
       <c r="G18">
-        <v>-1.409320250009314</v>
+        <v>-5.390999444274792</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.08507568145618483</v>
       </c>
       <c r="E19">
-        <v>-28.40476019186576</v>
+        <v>-29.77115023962216</v>
       </c>
       <c r="F19">
-        <v>-1.756452992428121</v>
+        <v>-2.107332856905935</v>
       </c>
       <c r="G19">
-        <v>-2.344145478297633</v>
+        <v>-5.082161961461722</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.25408281492419</v>
       </c>
       <c r="E20">
-        <v>-29.44383213834774</v>
+        <v>-30.60354716086808</v>
       </c>
       <c r="F20">
-        <v>-1.380705538518265</v>
+        <v>-1.767098341921497</v>
       </c>
       <c r="G20">
-        <v>-1.286403004681714</v>
+        <v>-4.161346961895598</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.493344530162759</v>
       </c>
       <c r="E21">
-        <v>-30.01940797743366</v>
+        <v>-30.88983502339599</v>
       </c>
       <c r="F21">
-        <v>-1.582072542097394</v>
+        <v>-1.368387715238636</v>
       </c>
       <c r="G21">
-        <v>-1.739421366821122</v>
+        <v>-4.180207139832826</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.591180596233292</v>
       </c>
       <c r="E22">
-        <v>-27.94954439919271</v>
+        <v>-32.97098129462705</v>
       </c>
       <c r="F22">
-        <v>-1.132693994854899</v>
+        <v>-1.138550552392691</v>
       </c>
       <c r="G22">
-        <v>-1.246232845108197</v>
+        <v>-3.280741848449463</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.50462153950643</v>
       </c>
       <c r="E23">
-        <v>-29.44725113622354</v>
+        <v>-32.61313675006694</v>
       </c>
       <c r="F23">
-        <v>-1.462563148528107</v>
+        <v>-0.9850780953086239</v>
       </c>
       <c r="G23">
-        <v>0.3721405839466795</v>
+        <v>-3.585212721696234</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.207439152678419</v>
       </c>
       <c r="E24">
-        <v>-31.19888526052346</v>
+        <v>-34.10456022941212</v>
       </c>
       <c r="F24">
-        <v>-1.100494525540679</v>
+        <v>-1.009493396138736</v>
       </c>
       <c r="G24">
-        <v>-0.1084248276250046</v>
+        <v>-3.837860315071254</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.692121551582694</v>
       </c>
       <c r="E25">
-        <v>-32.46186534007771</v>
+        <v>-32.53115778510607</v>
       </c>
       <c r="F25">
-        <v>-0.6185114373239951</v>
+        <v>-0.7646337904430222</v>
       </c>
       <c r="G25">
-        <v>-1.779038665289581</v>
+        <v>-4.014021064306952</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.954613557886415</v>
       </c>
       <c r="E26">
-        <v>-30.53883979577247</v>
+        <v>-33.12705741553842</v>
       </c>
       <c r="F26">
-        <v>-0.143329245484295</v>
+        <v>-0.5811338433748757</v>
       </c>
       <c r="G26">
-        <v>-1.043521520647544</v>
+        <v>-3.818043389473176</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.005539365840273</v>
       </c>
       <c r="E27">
-        <v>-32.80264885881393</v>
+        <v>-33.15049226852811</v>
       </c>
       <c r="F27">
-        <v>-0.4234060629426274</v>
+        <v>-1.026467472589501</v>
       </c>
       <c r="G27">
-        <v>-1.521120683416041</v>
+        <v>-3.391552428739947</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.865853095020896</v>
       </c>
       <c r="E28">
-        <v>-32.10314680003411</v>
+        <v>-32.85702903893504</v>
       </c>
       <c r="F28">
-        <v>0.1098322583222759</v>
+        <v>-1.192885655444519</v>
       </c>
       <c r="G28">
-        <v>-0.1424870306785658</v>
+        <v>-3.888558009459652</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.558171137318787</v>
       </c>
       <c r="E29">
-        <v>-32.51026793450869</v>
+        <v>-33.00048883126103</v>
       </c>
       <c r="F29">
-        <v>-0.8408510468072019</v>
+        <v>-1.068980116068575</v>
       </c>
       <c r="G29">
-        <v>-0.4060494926965628</v>
+        <v>-4.391072337956705</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.111034469669296</v>
       </c>
       <c r="E30">
-        <v>-31.18264388849495</v>
+        <v>-32.95667358099982</v>
       </c>
       <c r="F30">
-        <v>-0.4727088340224485</v>
+        <v>-0.8519834763334244</v>
       </c>
       <c r="G30">
-        <v>-0.9348925898674386</v>
+        <v>-3.098238093960521</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.552627950570495</v>
       </c>
       <c r="E31">
-        <v>-31.93029494716133</v>
+        <v>-32.43672098815012</v>
       </c>
       <c r="F31">
-        <v>-0.2381855967788664</v>
+        <v>-0.8011739049479112</v>
       </c>
       <c r="G31">
-        <v>-2.694811703999394</v>
+        <v>-4.2961589973458</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.912583652831959</v>
       </c>
       <c r="E32">
-        <v>-29.800576263724</v>
+        <v>-32.00550837195473</v>
       </c>
       <c r="F32">
-        <v>-1.130768869010792</v>
+        <v>-1.131898762148211</v>
       </c>
       <c r="G32">
-        <v>-0.3069714857972548</v>
+        <v>-4.536299349673452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.221222372951604</v>
       </c>
       <c r="E33">
-        <v>-31.15559304901014</v>
+        <v>-32.45267253784214</v>
       </c>
       <c r="F33">
-        <v>-0.3693368658270981</v>
+        <v>-1.178032199544921</v>
       </c>
       <c r="G33">
-        <v>-1.387857983278219</v>
+        <v>-3.557493523895916</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.501053738604211</v>
       </c>
       <c r="E34">
-        <v>-29.78094532890075</v>
+        <v>-31.02058791765646</v>
       </c>
       <c r="F34">
-        <v>-1.21824446674642</v>
+        <v>-1.126035577671196</v>
       </c>
       <c r="G34">
-        <v>-1.593601767452844</v>
+        <v>-4.017401131302548</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.776801521863726</v>
       </c>
       <c r="E35">
-        <v>-31.41167825414389</v>
+        <v>-30.79317474570227</v>
       </c>
       <c r="F35">
-        <v>-0.6245485789555978</v>
+        <v>-0.7848285593558714</v>
       </c>
       <c r="G35">
-        <v>-2.858749919104103</v>
+        <v>-4.205509639389476</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.071721127838715</v>
       </c>
       <c r="E36">
-        <v>-29.2526399657439</v>
+        <v>-31.44642070673074</v>
       </c>
       <c r="F36">
-        <v>-0.5606450040340327</v>
+        <v>-1.009276363879203</v>
       </c>
       <c r="G36">
-        <v>-2.619341197340629</v>
+        <v>-4.679586381704189</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.3961043561388806</v>
       </c>
       <c r="E37">
-        <v>-28.79270550315486</v>
+        <v>-30.29315196696033</v>
       </c>
       <c r="F37">
-        <v>-0.8860832204696661</v>
+        <v>-1.250947583441542</v>
       </c>
       <c r="G37">
-        <v>-2.694457475626692</v>
+        <v>-4.732015491409626</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2384048663205031</v>
       </c>
       <c r="E38">
-        <v>-29.75921544637494</v>
+        <v>-30.09583956173512</v>
       </c>
       <c r="F38">
-        <v>-1.175909093891546</v>
+        <v>-1.111327914434491</v>
       </c>
       <c r="G38">
-        <v>-1.378336854307275</v>
+        <v>-4.908126582462235</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8207490058322624</v>
       </c>
       <c r="E39">
-        <v>-29.18157462314153</v>
+        <v>-29.380809365583</v>
       </c>
       <c r="F39">
-        <v>-0.6622276986393362</v>
+        <v>-0.890227542585872</v>
       </c>
       <c r="G39">
-        <v>-2.80121594817711</v>
+        <v>-4.396468527185717</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.352776321243032</v>
       </c>
       <c r="E40">
-        <v>-27.91161390090446</v>
+        <v>-29.12796201936472</v>
       </c>
       <c r="F40">
-        <v>-0.2543660972577492</v>
+        <v>-1.399933602672047</v>
       </c>
       <c r="G40">
-        <v>0.1074922629918015</v>
+        <v>-4.707245989684799</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.833645726884215</v>
       </c>
       <c r="E41">
-        <v>-27.04774861377924</v>
+        <v>-28.60332019168008</v>
       </c>
       <c r="F41">
-        <v>-0.4668522764846559</v>
+        <v>-1.116193744558535</v>
       </c>
       <c r="G41">
-        <v>-2.469515837869833</v>
+        <v>-5.435784504330052</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.259492135462791</v>
       </c>
       <c r="E42">
-        <v>-26.51243770133253</v>
+        <v>-27.67626004977782</v>
       </c>
       <c r="F42">
-        <v>-0.2188092548599831</v>
+        <v>-1.672360447165526</v>
       </c>
       <c r="G42">
-        <v>-2.609098369442124</v>
+        <v>-5.267082414194332</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.637780788362825</v>
       </c>
       <c r="E43">
-        <v>-24.65546447890318</v>
+        <v>-28.55091669046332</v>
       </c>
       <c r="F43">
-        <v>-0.9937187956872254</v>
+        <v>-1.215099984085393</v>
       </c>
       <c r="G43">
-        <v>-0.9038694676189283</v>
+        <v>-4.62620714542898</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.972981072962399</v>
       </c>
       <c r="E44">
-        <v>-25.47716061606897</v>
+        <v>-26.99511416038809</v>
       </c>
       <c r="F44">
-        <v>-0.625840832103965</v>
+        <v>-1.045758492665896</v>
       </c>
       <c r="G44">
-        <v>-1.812663876331958</v>
+        <v>-4.152822307131975</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.264974060827807</v>
       </c>
       <c r="E45">
-        <v>-24.70523240824748</v>
+        <v>-25.76772562229713</v>
       </c>
       <c r="F45">
-        <v>-0.4905957713510982</v>
+        <v>-1.079973379871127</v>
       </c>
       <c r="G45">
-        <v>-2.367640419989841</v>
+        <v>-4.951196779928154</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.524034531846411</v>
       </c>
       <c r="E46">
-        <v>-22.94693010597125</v>
+        <v>-26.34906847303181</v>
       </c>
       <c r="F46">
-        <v>0.07295582665185031</v>
+        <v>-0.8401229118601411</v>
       </c>
       <c r="G46">
-        <v>-2.951163797832859</v>
+        <v>-4.456756872001384</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.758754497434443</v>
       </c>
       <c r="E47">
-        <v>-24.09824028073335</v>
+        <v>-24.65268399586247</v>
       </c>
       <c r="F47">
-        <v>-0.4696016278945475</v>
+        <v>-1.115359578583916</v>
       </c>
       <c r="G47">
-        <v>-2.968593820097122</v>
+        <v>-5.400411325242939</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.97217206471689</v>
       </c>
       <c r="E48">
-        <v>-21.17995577597034</v>
+        <v>-25.09347207034708</v>
       </c>
       <c r="F48">
-        <v>-0.4732456160994625</v>
+        <v>-1.092326822949076</v>
       </c>
       <c r="G48">
-        <v>-2.5925820577467</v>
+        <v>-4.959681708145306</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.174674496487137</v>
       </c>
       <c r="E49">
-        <v>-21.07940101063002</v>
+        <v>-24.16330086680155</v>
       </c>
       <c r="F49">
-        <v>-0.9521190130860371</v>
+        <v>-1.007038943524242</v>
       </c>
       <c r="G49">
-        <v>-3.201563530786713</v>
+        <v>-4.484383374526602</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.375171651570904</v>
       </c>
       <c r="E50">
-        <v>-19.75866703781895</v>
+        <v>-22.30236975808949</v>
       </c>
       <c r="F50">
-        <v>-0.2743405204414536</v>
+        <v>-1.310291824178099</v>
       </c>
       <c r="G50">
-        <v>-2.315966114667357</v>
+        <v>-4.617381231021283</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.576695503639671</v>
       </c>
       <c r="E51">
-        <v>-20.06752255056409</v>
+        <v>-22.36356302735514</v>
       </c>
       <c r="F51">
-        <v>-0.2966095213309127</v>
+        <v>-0.9816436840566171</v>
       </c>
       <c r="G51">
-        <v>-4.190489694277803</v>
+        <v>-4.616543662999847</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.786767368536772</v>
       </c>
       <c r="E52">
-        <v>-19.56701296086633</v>
+        <v>-22.47954630363959</v>
       </c>
       <c r="F52">
-        <v>-0.8881748481617349</v>
+        <v>-0.7775074482499293</v>
       </c>
       <c r="G52">
-        <v>-3.875511149489385</v>
+        <v>-4.182809228626693</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.010588091611452</v>
       </c>
       <c r="E53">
-        <v>-21.05277358346492</v>
+        <v>-20.96676427663724</v>
       </c>
       <c r="F53">
-        <v>-0.4762840677329311</v>
+        <v>-1.149924865200531</v>
       </c>
       <c r="G53">
-        <v>-2.571176070289773</v>
+        <v>-4.560178314648216</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.246369706404894</v>
       </c>
       <c r="E54">
-        <v>-20.02674817059903</v>
+        <v>-21.20306910730549</v>
       </c>
       <c r="F54">
-        <v>0.3266317466155597</v>
+        <v>-1.209113372865361</v>
       </c>
       <c r="G54">
-        <v>-3.900601774131521</v>
+        <v>-6.213146944588477</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.492917505823728</v>
       </c>
       <c r="E55">
-        <v>-18.1645943739049</v>
+        <v>-19.90605980982061</v>
       </c>
       <c r="F55">
-        <v>-0.4220897871395791</v>
+        <v>-1.171775540551576</v>
       </c>
       <c r="G55">
-        <v>-4.249533273970704</v>
+        <v>-5.337802288004243</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.74652091239876</v>
       </c>
       <c r="E56">
-        <v>-17.2624861237849</v>
+        <v>-21.38657645951831</v>
       </c>
       <c r="F56">
-        <v>0.1996935541779663</v>
+        <v>-0.8378854915051797</v>
       </c>
       <c r="G56">
-        <v>-3.54857160366758</v>
+        <v>-5.071727121921939</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.998414703151486</v>
       </c>
       <c r="E57">
-        <v>-16.96972933613703</v>
+        <v>-19.56159690595315</v>
       </c>
       <c r="F57">
-        <v>-0.3012500355213956</v>
+        <v>-0.9137299825380997</v>
       </c>
       <c r="G57">
-        <v>-4.194551733654488</v>
+        <v>-5.287899124545269</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.238371843975791</v>
       </c>
       <c r="E58">
-        <v>-18.09621894486309</v>
+        <v>-19.33041377938757</v>
       </c>
       <c r="F58">
-        <v>-0.03474270448832182</v>
+        <v>-0.9335718669373562</v>
       </c>
       <c r="G58">
-        <v>-4.393972375849106</v>
+        <v>-6.503273224013586</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.454658052319174</v>
       </c>
       <c r="E59">
-        <v>-16.34202849698583</v>
+        <v>-19.80808627466466</v>
       </c>
       <c r="F59">
-        <v>-0.4808185508958556</v>
+        <v>-1.024582108380729</v>
       </c>
       <c r="G59">
-        <v>-4.733028518344643</v>
+        <v>-5.710672342637896</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.634469140352013</v>
       </c>
       <c r="E60">
-        <v>-14.9928013657185</v>
+        <v>-19.06550257841286</v>
       </c>
       <c r="F60">
-        <v>0.5982376790128644</v>
+        <v>-0.993208521367101</v>
       </c>
       <c r="G60">
-        <v>-3.81766267673616</v>
+        <v>-6.783570493732599</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.764074119416629</v>
       </c>
       <c r="E61">
-        <v>-16.53613700685061</v>
+        <v>-17.7167237660723</v>
       </c>
       <c r="F61">
-        <v>0.289367639000624</v>
+        <v>-1.035123911948756</v>
       </c>
       <c r="G61">
-        <v>-3.968951297335314</v>
+        <v>-6.189317637796803</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.831259928134303</v>
       </c>
       <c r="E62">
-        <v>-16.76784996487509</v>
+        <v>-18.24154220424323</v>
       </c>
       <c r="F62">
-        <v>-0.03113433608172717</v>
+        <v>-0.9247729483848198</v>
       </c>
       <c r="G62">
-        <v>-5.558344210739411</v>
+        <v>-7.050996362394925</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.829279723309337</v>
       </c>
       <c r="E63">
-        <v>-14.67472587989374</v>
+        <v>-18.42233700052547</v>
       </c>
       <c r="F63">
-        <v>-0.4914108848754529</v>
+        <v>-0.8489632487828175</v>
       </c>
       <c r="G63">
-        <v>-5.683956240135977</v>
+        <v>-7.601993630314603</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.750764866938005</v>
       </c>
       <c r="E64">
-        <v>-15.69277665003212</v>
+        <v>-17.79244890842856</v>
       </c>
       <c r="F64">
-        <v>-0.6076631378169327</v>
+        <v>-1.044390029716471</v>
       </c>
       <c r="G64">
-        <v>-4.218245308079053</v>
+        <v>-7.227895363285881</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.58956689481689</v>
       </c>
       <c r="E65">
-        <v>-14.20058106586863</v>
+        <v>-17.72952576209198</v>
       </c>
       <c r="F65">
-        <v>-0.267100589340986</v>
+        <v>-1.616686702390774</v>
       </c>
       <c r="G65">
-        <v>-4.518078107025304</v>
+        <v>-6.828924967620614</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.34811977500009</v>
       </c>
       <c r="E66">
-        <v>-14.91041030962294</v>
+        <v>-17.92311802591989</v>
       </c>
       <c r="F66">
-        <v>-0.3429152591474051</v>
+        <v>-1.521915672938691</v>
       </c>
       <c r="G66">
-        <v>-5.103948661655665</v>
+        <v>-6.490156842586993</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.027238635354268</v>
       </c>
       <c r="E67">
-        <v>-12.84919385249964</v>
+        <v>-17.05581109854884</v>
       </c>
       <c r="F67">
-        <v>-0.4057320160364972</v>
+        <v>-1.354027137943704</v>
       </c>
       <c r="G67">
-        <v>-4.660355422666562</v>
+        <v>-7.161148144123096</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.628039108883093</v>
       </c>
       <c r="E68">
-        <v>-13.20544437420906</v>
+        <v>-17.00761002121119</v>
       </c>
       <c r="F68">
-        <v>-0.1242386903193776</v>
+        <v>-1.487129212225529</v>
       </c>
       <c r="G68">
-        <v>-4.812471679650534</v>
+        <v>-6.270088327863941</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.162049150413683</v>
       </c>
       <c r="E69">
-        <v>-14.99037410365039</v>
+        <v>-16.82967722050181</v>
       </c>
       <c r="F69">
-        <v>-0.4050585533380212</v>
+        <v>-1.539253402679285</v>
       </c>
       <c r="G69">
-        <v>-4.952888468698721</v>
+        <v>-7.300326789139596</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.637104867392011</v>
       </c>
       <c r="E70">
-        <v>-14.61372280653641</v>
+        <v>-15.77695645336071</v>
       </c>
       <c r="F70">
-        <v>-0.6843376529874577</v>
+        <v>-1.579629686626538</v>
       </c>
       <c r="G70">
-        <v>-4.864116190063164</v>
+        <v>-7.857723341586685</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.056945969142824</v>
       </c>
       <c r="E71">
-        <v>-12.0850908477634</v>
+        <v>-16.96676771413602</v>
       </c>
       <c r="F71">
-        <v>-0.566527240961312</v>
+        <v>-2.023391902878053</v>
       </c>
       <c r="G71">
-        <v>-4.502740349541861</v>
+        <v>-6.551216544513311</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.435523189575068</v>
       </c>
       <c r="E72">
-        <v>-13.81089229208657</v>
+        <v>-16.86719109918135</v>
       </c>
       <c r="F72">
-        <v>-1.207001035988223</v>
+        <v>-1.598118847057023</v>
       </c>
       <c r="G72">
-        <v>-3.749432333171781</v>
+        <v>-6.789493059702354</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.783669153963867</v>
       </c>
       <c r="E73">
-        <v>-12.72006441617092</v>
+        <v>-16.80747864091621</v>
       </c>
       <c r="F73">
-        <v>-0.6646896065604563</v>
+        <v>-1.790345644713663</v>
       </c>
       <c r="G73">
-        <v>-4.399004405068798</v>
+        <v>-7.108609786414862</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.106787314966501</v>
       </c>
       <c r="E74">
-        <v>-14.48088907846942</v>
+        <v>-16.4374796721195</v>
       </c>
       <c r="F74">
-        <v>-0.9600663699484956</v>
+        <v>-2.141160896534059</v>
       </c>
       <c r="G74">
-        <v>-4.334577878329042</v>
+        <v>-5.939871341958258</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.420869519885414</v>
       </c>
       <c r="E75">
-        <v>-16.1635975641356</v>
+        <v>-16.96875118575138</v>
       </c>
       <c r="F75">
-        <v>-1.402323442629124</v>
+        <v>-1.68091002712982</v>
       </c>
       <c r="G75">
-        <v>-3.39708103979053</v>
+        <v>-5.726182248489382</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.7383650756005882</v>
       </c>
       <c r="E76">
-        <v>-13.00876821958193</v>
+        <v>-16.57395429328866</v>
       </c>
       <c r="F76">
-        <v>-1.419070546411521</v>
+        <v>-2.132897103323731</v>
       </c>
       <c r="G76">
-        <v>-4.661173127414762</v>
+        <v>-5.417321591857537</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.06262283750223449</v>
       </c>
       <c r="E77">
-        <v>-14.01877641988269</v>
+        <v>-16.49011412551066</v>
       </c>
       <c r="F77">
-        <v>-1.918329236813589</v>
+        <v>-2.443395713649875</v>
       </c>
       <c r="G77">
-        <v>-2.204953591098976</v>
+        <v>-6.27081995842812</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5948995459362065</v>
       </c>
       <c r="E78">
-        <v>-13.66418784813409</v>
+        <v>-17.25289934431067</v>
       </c>
       <c r="F78">
-        <v>-1.764336565000564</v>
+        <v>-2.973645285325478</v>
       </c>
       <c r="G78">
-        <v>-3.793578457937962</v>
+        <v>-5.590804109751965</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.225244010659835</v>
       </c>
       <c r="E79">
-        <v>-16.16419079423061</v>
+        <v>-17.15872067037315</v>
       </c>
       <c r="F79">
-        <v>-1.592547247905794</v>
+        <v>-2.59930274253077</v>
       </c>
       <c r="G79">
-        <v>-2.282132339256005</v>
+        <v>-4.602751930283244</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.8300427903422</v>
       </c>
       <c r="E80">
-        <v>-14.99620224969826</v>
+        <v>-17.94760801335337</v>
       </c>
       <c r="F80">
-        <v>-1.957023106565757</v>
+        <v>-2.558442692020281</v>
       </c>
       <c r="G80">
-        <v>-2.404466928568693</v>
+        <v>-5.140804965144372</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.403802077813132</v>
       </c>
       <c r="E81">
-        <v>-15.19048284157533</v>
+        <v>-19.67148032774928</v>
       </c>
       <c r="F81">
-        <v>-1.606313885772919</v>
+        <v>-2.410693425322156</v>
       </c>
       <c r="G81">
-        <v>-2.605516359168633</v>
+        <v>-4.283506092294705</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.940826585461957</v>
       </c>
       <c r="E82">
-        <v>-15.66035730461121</v>
+        <v>-19.84627942444535</v>
       </c>
       <c r="F82">
-        <v>-2.073356539512711</v>
+        <v>-2.57813132845002</v>
       </c>
       <c r="G82">
-        <v>-2.674044651831546</v>
+        <v>-4.103935481153557</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.444935773116428</v>
       </c>
       <c r="E83">
-        <v>-17.22821010402085</v>
+        <v>-20.96747977553045</v>
       </c>
       <c r="F83">
-        <v>-2.950833703787185</v>
+        <v>-3.001360801888344</v>
       </c>
       <c r="G83">
-        <v>-1.726063315570163</v>
+        <v>-3.993899568519262</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.913509573523625</v>
       </c>
       <c r="E84">
-        <v>-17.63735773061386</v>
+        <v>-20.34729620323198</v>
       </c>
       <c r="F84">
-        <v>-2.276671863223224</v>
+        <v>-3.31826020713592</v>
       </c>
       <c r="G84">
-        <v>-2.205278024561824</v>
+        <v>-4.422754258767529</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.340738872792452</v>
       </c>
       <c r="E85">
-        <v>-19.50001418792284</v>
+        <v>-21.16338156110227</v>
       </c>
       <c r="F85">
-        <v>-2.404736635328625</v>
+        <v>-3.011782492182964</v>
       </c>
       <c r="G85">
-        <v>-1.094755523413305</v>
+        <v>-4.567302608648728</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.728150154469733</v>
       </c>
       <c r="E86">
-        <v>-19.92255704063055</v>
+        <v>-22.53151959982563</v>
       </c>
       <c r="F86">
-        <v>-2.723788139088674</v>
+        <v>-3.017405450113167</v>
       </c>
       <c r="G86">
-        <v>-3.106845512362626</v>
+        <v>-4.357460369096484</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.071736152179576</v>
       </c>
       <c r="E87">
-        <v>-20.89101196343692</v>
+        <v>-23.01258392213446</v>
       </c>
       <c r="F87">
-        <v>-3.365938549738851</v>
+        <v>-3.20017643386685</v>
       </c>
       <c r="G87">
-        <v>-2.279715641012337</v>
+        <v>-3.38422950200708</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.363110822894829</v>
       </c>
       <c r="E88">
-        <v>-21.33401446171128</v>
+        <v>-23.63727332607056</v>
       </c>
       <c r="F88">
-        <v>-3.188878330860068</v>
+        <v>-3.151484169562893</v>
       </c>
       <c r="G88">
-        <v>-1.535250091777651</v>
+        <v>-4.908113340280078</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.598963038502593</v>
       </c>
       <c r="E89">
-        <v>-21.88635243642684</v>
+        <v>-25.60266727319156</v>
       </c>
       <c r="F89">
-        <v>-3.469047097100111</v>
+        <v>-3.679126869021885</v>
       </c>
       <c r="G89">
-        <v>-1.748406187414705</v>
+        <v>-4.201404562920779</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.772766143170871</v>
       </c>
       <c r="E90">
-        <v>-24.30633724680782</v>
+        <v>-25.47641341785771</v>
       </c>
       <c r="F90">
-        <v>-3.916554362379682</v>
+        <v>-3.862798288142411</v>
       </c>
       <c r="G90">
-        <v>-3.119584491597741</v>
+        <v>-4.55820854005235</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.875138340207797</v>
       </c>
       <c r="E91">
-        <v>-27.42928613434749</v>
+        <v>-26.58507442441556</v>
       </c>
       <c r="F91">
-        <v>-3.843542059496934</v>
+        <v>-4.088375157435759</v>
       </c>
       <c r="G91">
-        <v>-2.75306406330841</v>
+        <v>-5.278387927210943</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.900478199608984</v>
       </c>
       <c r="E92">
-        <v>-28.18313667393037</v>
+        <v>-29.09686045988004</v>
       </c>
       <c r="F92">
-        <v>-3.985708958267594</v>
+        <v>-3.947372943233435</v>
       </c>
       <c r="G92">
-        <v>-2.364866182827932</v>
+        <v>-4.78532520622851</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.844053629788887</v>
       </c>
       <c r="E93">
-        <v>-31.38132162863348</v>
+        <v>-30.34752761860743</v>
       </c>
       <c r="F93">
-        <v>-3.800543164352417</v>
+        <v>-3.731259343149669</v>
       </c>
       <c r="G93">
-        <v>-3.172549909680541</v>
+        <v>-5.934246725087037</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.701645858221639</v>
       </c>
       <c r="E94">
-        <v>-32.28927613869737</v>
+        <v>-32.30686246750616</v>
       </c>
       <c r="F94">
-        <v>-3.991837220313504</v>
+        <v>-4.292549498142975</v>
       </c>
       <c r="G94">
-        <v>-3.361393358877187</v>
+        <v>-5.599471117973777</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.474606295473543</v>
       </c>
       <c r="E95">
-        <v>-32.83644259609617</v>
+        <v>-34.21001933210274</v>
       </c>
       <c r="F95">
-        <v>-3.184449878724702</v>
+        <v>-4.309161578038716</v>
       </c>
       <c r="G95">
-        <v>-3.600858359914829</v>
+        <v>-5.352921549482095</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.1633870864354</v>
       </c>
       <c r="E96">
-        <v>-35.51769092163868</v>
+        <v>-35.2354967996137</v>
       </c>
       <c r="F96">
-        <v>-4.477198390798804</v>
+        <v>-4.33373095520575</v>
       </c>
       <c r="G96">
-        <v>-3.27525627449089</v>
+        <v>-5.673465121322027</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.78188381556514</v>
       </c>
       <c r="E97">
-        <v>-35.63178129578793</v>
+        <v>-37.27141946516716</v>
       </c>
       <c r="F97">
-        <v>-5.04374950716729</v>
+        <v>-4.58924750753848</v>
       </c>
       <c r="G97">
-        <v>-4.194584839109881</v>
+        <v>-6.27313734030561</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.329716619407715</v>
       </c>
       <c r="E98">
-        <v>-39.38345672184154</v>
+        <v>-40.82266689587829</v>
       </c>
       <c r="F98">
-        <v>-4.534952994489389</v>
+        <v>-4.950043758195207</v>
       </c>
       <c r="G98">
-        <v>-3.682334196181833</v>
+        <v>-7.057511516016211</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.838865673106678</v>
       </c>
       <c r="E99">
-        <v>-40.32128104646004</v>
+        <v>-42.34022872719574</v>
       </c>
       <c r="F99">
-        <v>-5.201471489027718</v>
+        <v>-4.95261915245051</v>
       </c>
       <c r="G99">
-        <v>-4.776820414738123</v>
+        <v>-7.006747610717026</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.301229923420343</v>
       </c>
       <c r="E100">
-        <v>-43.83607652564642</v>
+        <v>-44.08776231828173</v>
       </c>
       <c r="F100">
-        <v>-4.68005562733557</v>
+        <v>-5.299840946477563</v>
       </c>
       <c r="G100">
-        <v>-5.541523328854374</v>
+        <v>-7.128198284370729</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.777767344818223</v>
       </c>
       <c r="E101">
-        <v>-45.30607353022431</v>
+        <v>-45.7657430770839</v>
       </c>
       <c r="F101">
-        <v>-4.960462135020216</v>
+        <v>-4.985563324059847</v>
       </c>
       <c r="G101">
-        <v>-4.603506734666198</v>
+        <v>-7.77416517217548</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.216743420957588</v>
       </c>
       <c r="E102">
-        <v>-46.78474256252689</v>
+        <v>-48.68976289417762</v>
       </c>
       <c r="F102">
-        <v>-4.978052516818664</v>
+        <v>-5.375004519505381</v>
       </c>
       <c r="G102">
-        <v>-6.01712954320823</v>
+        <v>-7.316747095014381</v>
       </c>
     </row>
   </sheetData>
